--- a/data/trans_orig/P16A11-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A11-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>38714</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65611</t>
+          <t>67082</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>22055</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41636</t>
+          <t>42709</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63561</t>
+          <t>65721</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99263</t>
+          <t>98086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408165</t>
+          <t>406694</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435289</t>
+          <t>435062</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265044</t>
+          <t>263971</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285416</t>
+          <t>284625</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>681194</t>
+          <t>682371</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>716896</t>
+          <t>714736</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35847</t>
+          <t>36099</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61010</t>
+          <t>63893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13591</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33632</t>
+          <t>31276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53830</t>
+          <t>54083</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85527</t>
+          <t>86025</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>305924</t>
+          <t>303041</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>331087</t>
+          <t>330835</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>338233</t>
+          <t>340589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358274</t>
+          <t>358911</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>653272</t>
+          <t>652774</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>684969</t>
+          <t>684716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50252</t>
+          <t>50066</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80438</t>
+          <t>78829</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,47 +1434,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>9,23%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>23545</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>15530</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>32954</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>14,03%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>9,26%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>23545</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>15961</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>33800</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71035</t>
+          <t>69945</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104703</t>
+          <t>107507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>461951</t>
+          <t>463560</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>492137</t>
+          <t>492323</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,49 +1547,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>90,77%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>144237</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>134828</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>152252</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>85,97%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>80,36%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>90,74%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>144237</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>133982</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>151821</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>85,97%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>79,85%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>90,49%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>608</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>605468</t>
+          <t>602664</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639136</t>
+          <t>640226</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>179478</t>
+          <t>178857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>226633</t>
+          <t>229539</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>83185</t>
+          <t>82509</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118050</t>
+          <t>117695</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>273161</t>
+          <t>271886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>337536</t>
+          <t>333236</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1011701</t>
+          <t>1008795</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1058856</t>
+          <t>1059477</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>596235</t>
+          <t>596590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>631100</t>
+          <t>631776</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1615084</t>
+          <t>1619384</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1679459</t>
+          <t>1680734</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30247</t>
+          <t>31052</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55436</t>
+          <t>55400</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65725</t>
+          <t>67954</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>100301</t>
+          <t>102704</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105846</t>
+          <t>106252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145124</t>
+          <t>148223</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>294101</t>
+          <t>294137</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>319290</t>
+          <t>318485</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>468451</t>
+          <t>466048</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>503027</t>
+          <t>500798</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>773165</t>
+          <t>770066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>812443</t>
+          <t>812037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,43%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275919</t>
+          <t>279503</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>335540</t>
+          <t>337113</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>283430</t>
+          <t>282578</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>342547</t>
+          <t>348236</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287525</t>
+          <t>287769</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>913220</t>
+          <t>911647</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>972841</t>
+          <t>969257</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1204413</t>
+          <t>1198724</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1263530</t>
+          <t>1264382</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>377788</t>
+          <t>377849</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>450248</t>
+          <t>452533</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>521125</t>
+          <t>520147</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>605210</t>
+          <t>610948</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>919745</t>
+          <t>914348</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1032662</t>
+          <t>1031247</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2818924</t>
+          <t>2816639</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2891384</t>
+          <t>2891323</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2772914</t>
+          <t>2767176</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2856999</t>
+          <t>2857977</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5614634</t>
+          <t>5616049</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5727551</t>
+          <t>5732948</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55401</t>
+          <t>56524</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89591</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>18572</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39983</t>
+          <t>42348</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80049</t>
+          <t>81188</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121593</t>
+          <t>124021</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>347620</t>
+          <t>347211</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>381810</t>
+          <t>380687</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274471</t>
+          <t>272106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>296242</t>
+          <t>295882</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>630072</t>
+          <t>627644</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>671616</t>
+          <t>670477</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42151</t>
+          <t>42288</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69140</t>
+          <t>70568</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>21238</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44806</t>
+          <t>46452</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71449</t>
+          <t>69370</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106255</t>
+          <t>105768</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>347878</t>
+          <t>346450</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>374867</t>
+          <t>374730</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>290509</t>
+          <t>288863</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313987</t>
+          <t>314077</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>646078</t>
+          <t>646565</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>680884</t>
+          <t>682963</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110528</t>
+          <t>112918</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154469</t>
+          <t>157051</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,82 +4069,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>57831</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>44262</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>72125</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>22,52%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>17,24%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>28,08%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>191099</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>165575</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>217562</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>21,59%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>18,71%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>24,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>57831</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>44789</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>71698</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>22,52%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>17,44%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>27,92%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>191099</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>168830</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>220387</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>21,59%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>19,07%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>473860</t>
+          <t>471278</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517801</t>
+          <t>515411</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,82 +4182,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>75,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>82,03%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>198981</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>184687</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>212550</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>77,48%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>71,92%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>82,76%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>694043</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>667580</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>719567</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>78,41%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>75,42%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>198981</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>185114</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>212023</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>77,48%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>72,08%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>82,56%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>694043</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>664755</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>716312</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>78,41%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>75,1%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>189244</t>
+          <t>187774</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242921</t>
+          <t>245670</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67400</t>
+          <t>65146</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101179</t>
+          <t>101066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>266722</t>
+          <t>263760</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>329948</t>
+          <t>328421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>915209</t>
+          <t>912460</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>968886</t>
+          <t>970356</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>665478</t>
+          <t>665591</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>699257</t>
+          <t>701511</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1594840</t>
+          <t>1596367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1658066</t>
+          <t>1661028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,3%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75723</t>
+          <t>75978</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111656</t>
+          <t>110956</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>167418</t>
+          <t>169032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>216166</t>
+          <t>217922</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255291</t>
+          <t>252845</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>316675</t>
+          <t>314149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>398940</t>
+          <t>399640</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>434873</t>
+          <t>434618</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>543139</t>
+          <t>541383</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>591887</t>
+          <t>590273</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>953226</t>
+          <t>955752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1014610</t>
+          <t>1017056</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,09%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>318851</t>
+          <t>317295</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>379797</t>
+          <t>381452</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>321567</t>
+          <t>319479</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>388253</t>
+          <t>386224</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255835</t>
+          <t>256035</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264845</t>
+          <t>264836</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>726503</t>
+          <t>724848</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>787449</t>
+          <t>789005</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>983888</t>
+          <t>985917</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1050574</t>
+          <t>1052662</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,72%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>523494</t>
+          <t>528061</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>615583</t>
+          <t>620294</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>689966</t>
+          <t>691203</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>792644</t>
+          <t>790671</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1241991</t>
+          <t>1247986</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1373300</t>
+          <t>1380166</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2801542</t>
+          <t>2796831</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2893631</t>
+          <t>2889064</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2746200</t>
+          <t>2748173</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2848878</t>
+          <t>2847641</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5582669</t>
+          <t>5575803</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5713978</t>
+          <t>5707983</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,06%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42235</t>
+          <t>41222</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69133</t>
+          <t>69289</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22230</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46472</t>
+          <t>48352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67841</t>
+          <t>68225</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105351</t>
+          <t>105900</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>359959</t>
+          <t>359803</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>386857</t>
+          <t>387870</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>300583</t>
+          <t>298703</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>324825</t>
+          <t>325231</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>670796</t>
+          <t>670247</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>708306</t>
+          <t>707922</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41318</t>
+          <t>40220</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68958</t>
+          <t>69309</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17904</t>
+          <t>17764</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41236</t>
+          <t>40801</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64726</t>
+          <t>65826</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100010</t>
+          <t>100649</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>308269</t>
+          <t>307918</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335909</t>
+          <t>337007</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>331037</t>
+          <t>331472</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354369</t>
+          <t>354509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>649490</t>
+          <t>648851</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>684774</t>
+          <t>683674</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68694</t>
+          <t>69417</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100401</t>
+          <t>102231</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23364</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46716</t>
+          <t>48576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98357</t>
+          <t>98415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>139705</t>
+          <t>138614</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>421513</t>
+          <t>419683</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>453220</t>
+          <t>452497</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119407</t>
+          <t>117547</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142759</t>
+          <t>141510</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>548331</t>
+          <t>549422</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>589679</t>
+          <t>589621</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>179555</t>
+          <t>181769</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>230516</t>
+          <t>233090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71085</t>
+          <t>71525</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108815</t>
+          <t>107696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>262028</t>
+          <t>264143</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>324640</t>
+          <t>325378</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>919122</t>
+          <t>916548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>970083</t>
+          <t>967869</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>717061</t>
+          <t>718180</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>754791</t>
+          <t>754351</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1650874</t>
+          <t>1650136</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1713486</t>
+          <t>1711371</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88887</t>
+          <t>89334</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>124364</t>
+          <t>125035</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123767</t>
+          <t>121072</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>169043</t>
+          <t>166124</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>223153</t>
+          <t>221618</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>279136</t>
+          <t>282641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>496342</t>
+          <t>495671</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>531819</t>
+          <t>531372</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>569201</t>
+          <t>572120</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>614477</t>
+          <t>617172</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1079814</t>
+          <t>1076309</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1135797</t>
+          <t>1137332</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>267371</t>
+          <t>266045</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>328583</t>
+          <t>331415</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>266403</t>
+          <t>267019</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>333456</t>
+          <t>334448</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>281814</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>753442</t>
+          <t>750610</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>814654</t>
+          <t>815980</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1035714</t>
+          <t>1034722</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1102767</t>
+          <t>1102151</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>461185</t>
+          <t>464976</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>544036</t>
+          <t>547492</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>575732</t>
+          <t>577915</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>672363</t>
+          <t>673124</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1064385</t>
+          <t>1062825</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1193664</t>
+          <t>1188548</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2841686</t>
+          <t>2838230</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2924537</t>
+          <t>2920746</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2859233</t>
+          <t>2858472</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2955864</t>
+          <t>2953681</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5723654</t>
+          <t>5728770</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5852933</t>
+          <t>5854493</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87403</t>
+          <t>88599</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>120310</t>
+          <t>122833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41839</t>
+          <t>41276</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62476</t>
+          <t>61919</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134308</t>
+          <t>136360</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174937</t>
+          <t>174423</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>384902</t>
+          <t>382379</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>417809</t>
+          <t>416613</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>384991</t>
+          <t>385548</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>405628</t>
+          <t>406191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>777742</t>
+          <t>778256</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>818371</t>
+          <t>816319</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,69%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77203</t>
+          <t>79181</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110440</t>
+          <t>110721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37817</t>
+          <t>38524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57579</t>
+          <t>58137</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>123460</t>
+          <t>123585</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159555</t>
+          <t>161252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340889</t>
+          <t>340608</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>374126</t>
+          <t>372148</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325001</t>
+          <t>324443</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>344763</t>
+          <t>344056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>674354</t>
+          <t>672657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710449</t>
+          <t>710324</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,18%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31836</t>
+          <t>33183</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148034</t>
+          <t>150286</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31441</t>
+          <t>31598</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48152</t>
+          <t>48146</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54661</t>
+          <t>54391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>188865</t>
+          <t>188488</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520230</t>
+          <t>517978</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636428</t>
+          <t>635081</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118759</t>
+          <t>118765</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135470</t>
+          <t>135313</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646310</t>
+          <t>646687</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>780514</t>
+          <t>780784</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>196957</t>
+          <t>197248</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>243798</t>
+          <t>244480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>147372</t>
+          <t>148109</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>625686</t>
+          <t>643615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>372860</t>
+          <t>369577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1018769</t>
+          <t>1037668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>791021</t>
+          <t>790339</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>837862</t>
+          <t>837571</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>351842</t>
+          <t>333913</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>830156</t>
+          <t>829419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>993578</t>
+          <t>974679</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1639487</t>
+          <t>1642770</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,63%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80121</t>
+          <t>77964</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111850</t>
+          <t>111577</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>149354</t>
+          <t>155355</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>238759</t>
+          <t>240366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>251881</t>
+          <t>243384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>335695</t>
+          <t>331772</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>362199</t>
+          <t>362472</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>393928</t>
+          <t>396085</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>600237</t>
+          <t>598630</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>689642</t>
+          <t>683641</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>977350</t>
+          <t>981273</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1061164</t>
+          <t>1069661</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,46%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>828</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7506</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>203211</t>
+          <t>203636</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>244452</t>
+          <t>243620</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>204952</t>
+          <t>202645</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>249119</t>
+          <t>249277</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233155</t>
+          <t>233001</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239619</t>
+          <t>239679</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>515700</t>
+          <t>516532</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>556941</t>
+          <t>556516</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>751540</t>
+          <t>751382</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>795707</t>
+          <t>798014</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,75%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>462596</t>
+          <t>463724</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>668663</t>
+          <t>668754</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>712545</t>
+          <t>714036</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1395965</t>
+          <t>1409344</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1287620</t>
+          <t>1297587</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2107594</t>
+          <t>2021755</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2705517</t>
+          <t>2705426</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2911584</t>
+          <t>2910456</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2177669</t>
+          <t>2164290</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2861089</t>
+          <t>2859598</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4840220</t>
+          <t>4926059</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5660194</t>
+          <t>5650227</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A11-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A11-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38714</t>
+          <t>39320</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67082</t>
+          <t>67496</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>20886</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42709</t>
+          <t>41129</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65721</t>
+          <t>66281</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98086</t>
+          <t>99161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406694</t>
+          <t>406280</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435062</t>
+          <t>434456</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>263971</t>
+          <t>265551</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284625</t>
+          <t>285794</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>682371</t>
+          <t>681296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>714736</t>
+          <t>714176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36099</t>
+          <t>36621</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63893</t>
+          <t>62364</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31276</t>
+          <t>32731</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54083</t>
+          <t>54951</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86025</t>
+          <t>87394</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>303041</t>
+          <t>304570</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>330835</t>
+          <t>330313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340589</t>
+          <t>339134</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358911</t>
+          <t>358723</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>652774</t>
+          <t>651405</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>684716</t>
+          <t>683848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50066</t>
+          <t>49701</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78829</t>
+          <t>80962</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15530</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32954</t>
+          <t>34047</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69945</t>
+          <t>71037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107507</t>
+          <t>106209</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>463560</t>
+          <t>461427</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>492323</t>
+          <t>492688</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>134828</t>
+          <t>133735</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>152252</t>
+          <t>152827</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>602664</t>
+          <t>603962</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640226</t>
+          <t>639134</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>178857</t>
+          <t>177326</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>229539</t>
+          <t>231269</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82509</t>
+          <t>82244</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117695</t>
+          <t>119487</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>271886</t>
+          <t>271797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>333236</t>
+          <t>333143</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1008795</t>
+          <t>1007065</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1059477</t>
+          <t>1061008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>596590</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>631776</t>
+          <t>632041</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1619384</t>
+          <t>1619477</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1680734</t>
+          <t>1680823</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31052</t>
+          <t>30588</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55400</t>
+          <t>55916</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67954</t>
+          <t>65899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102704</t>
+          <t>101109</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>106252</t>
+          <t>105129</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148223</t>
+          <t>148139</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>294137</t>
+          <t>293621</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>318485</t>
+          <t>318949</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>466048</t>
+          <t>467643</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>500798</t>
+          <t>502853</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>770066</t>
+          <t>770150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>812037</t>
+          <t>813160</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,55%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>279503</t>
+          <t>279327</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>337113</t>
+          <t>337935</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>282578</t>
+          <t>279991</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>348236</t>
+          <t>341166</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287769</t>
+          <t>287202</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>296432</t>
+          <t>296458</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>911647</t>
+          <t>910825</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>969257</t>
+          <t>969433</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1198724</t>
+          <t>1205794</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1264382</t>
+          <t>1266969</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>377849</t>
+          <t>373272</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>452533</t>
+          <t>450695</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>520147</t>
+          <t>519828</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>610948</t>
+          <t>606409</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>914348</t>
+          <t>918358</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1031247</t>
+          <t>1032889</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2816639</t>
+          <t>2818477</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2891323</t>
+          <t>2895900</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2767176</t>
+          <t>2771715</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2857977</t>
+          <t>2858296</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5616049</t>
+          <t>5614407</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5732948</t>
+          <t>5728938</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56524</t>
+          <t>56486</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>87184</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18572</t>
+          <t>19169</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42348</t>
+          <t>42867</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81188</t>
+          <t>80151</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>124021</t>
+          <t>121062</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>347211</t>
+          <t>350027</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>380687</t>
+          <t>380725</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272106</t>
+          <t>271587</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>295882</t>
+          <t>295285</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>627644</t>
+          <t>630603</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>670477</t>
+          <t>671514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42288</t>
+          <t>42616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70568</t>
+          <t>71011</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>22704</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46452</t>
+          <t>46575</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69370</t>
+          <t>70038</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105768</t>
+          <t>106230</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346450</t>
+          <t>346007</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>374730</t>
+          <t>374402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>288863</t>
+          <t>288740</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>314077</t>
+          <t>312611</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>646565</t>
+          <t>646103</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>682963</t>
+          <t>682295</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112918</t>
+          <t>113185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157051</t>
+          <t>155245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44262</t>
+          <t>45280</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72125</t>
+          <t>73369</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>165575</t>
+          <t>163413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217562</t>
+          <t>216239</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>471278</t>
+          <t>473084</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515411</t>
+          <t>515144</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>184687</t>
+          <t>183443</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>212550</t>
+          <t>211532</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>667580</t>
+          <t>668903</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>719567</t>
+          <t>721729</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>187774</t>
+          <t>188494</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>245670</t>
+          <t>245937</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65146</t>
+          <t>65616</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101066</t>
+          <t>100258</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>263760</t>
+          <t>265348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>328421</t>
+          <t>331075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>912460</t>
+          <t>912193</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>970356</t>
+          <t>969636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>665591</t>
+          <t>666399</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>701511</t>
+          <t>701041</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1596367</t>
+          <t>1593713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1661028</t>
+          <t>1659440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,21%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75978</t>
+          <t>75766</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110956</t>
+          <t>110816</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>169032</t>
+          <t>167887</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>217922</t>
+          <t>214045</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>252845</t>
+          <t>254223</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>314149</t>
+          <t>314472</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>399640</t>
+          <t>399780</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>434618</t>
+          <t>434830</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>541383</t>
+          <t>545260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>590273</t>
+          <t>591418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>955752</t>
+          <t>955429</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1017056</t>
+          <t>1015678</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>9729</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>317295</t>
+          <t>319687</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>381452</t>
+          <t>381532</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>319479</t>
+          <t>319423</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>386224</t>
+          <t>386823</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>256035</t>
+          <t>256112</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264836</t>
+          <t>264839</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>724848</t>
+          <t>724768</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>789005</t>
+          <t>786613</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>985917</t>
+          <t>985318</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1052662</t>
+          <t>1052718</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>528061</t>
+          <t>524030</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>620294</t>
+          <t>616049</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>691203</t>
+          <t>691066</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>790671</t>
+          <t>790862</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1247986</t>
+          <t>1241084</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1380166</t>
+          <t>1367020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2796831</t>
+          <t>2801076</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2889064</t>
+          <t>2893095</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2748173</t>
+          <t>2747982</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2847641</t>
+          <t>2847778</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5575803</t>
+          <t>5588949</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5707983</t>
+          <t>5714885</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,16%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41222</t>
+          <t>40121</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69289</t>
+          <t>69669</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>21573</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48352</t>
+          <t>46441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68225</t>
+          <t>68882</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105900</t>
+          <t>106172</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>359803</t>
+          <t>359423</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>387870</t>
+          <t>388971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298703</t>
+          <t>300614</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>325231</t>
+          <t>325482</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>670247</t>
+          <t>669975</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>707922</t>
+          <t>707265</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40220</t>
+          <t>41358</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69309</t>
+          <t>68533</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17764</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40801</t>
+          <t>41623</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65826</t>
+          <t>64962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100649</t>
+          <t>101258</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>307918</t>
+          <t>308694</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>337007</t>
+          <t>335869</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>331472</t>
+          <t>330650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354509</t>
+          <t>354244</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>648851</t>
+          <t>648242</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>683674</t>
+          <t>684538</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69417</t>
+          <t>68393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102231</t>
+          <t>101423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24613</t>
+          <t>23631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48576</t>
+          <t>47326</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98415</t>
+          <t>101004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>138614</t>
+          <t>141372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>419683</t>
+          <t>420491</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452497</t>
+          <t>453521</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117547</t>
+          <t>118797</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141510</t>
+          <t>142492</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>549422</t>
+          <t>546664</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>589621</t>
+          <t>587032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>181769</t>
+          <t>179233</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>233090</t>
+          <t>231819</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71525</t>
+          <t>71258</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107696</t>
+          <t>109407</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>264143</t>
+          <t>265579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>325378</t>
+          <t>326860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>916548</t>
+          <t>917819</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>967869</t>
+          <t>970405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>718180</t>
+          <t>716469</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>754351</t>
+          <t>754618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1650136</t>
+          <t>1648654</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1711371</t>
+          <t>1709935</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89334</t>
+          <t>88603</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>125035</t>
+          <t>125234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121072</t>
+          <t>121983</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>166124</t>
+          <t>167025</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>221618</t>
+          <t>224707</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>282641</t>
+          <t>278076</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>495671</t>
+          <t>495472</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>531372</t>
+          <t>532103</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>572120</t>
+          <t>571219</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>617172</t>
+          <t>616261</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1076309</t>
+          <t>1080874</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1137332</t>
+          <t>1134243</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>266045</t>
+          <t>268879</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>331415</t>
+          <t>331302</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>267019</t>
+          <t>268725</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>334448</t>
+          <t>336577</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281814</t>
+          <t>281506</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>750610</t>
+          <t>750723</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>815980</t>
+          <t>813146</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1034722</t>
+          <t>1032593</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1102151</t>
+          <t>1100445</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,37%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>464976</t>
+          <t>460493</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>547492</t>
+          <t>546896</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>577915</t>
+          <t>582835</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>673124</t>
+          <t>682429</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1062825</t>
+          <t>1071286</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1188548</t>
+          <t>1196613</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2838230</t>
+          <t>2838826</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2920746</t>
+          <t>2925229</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2858472</t>
+          <t>2849167</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2953681</t>
+          <t>2948761</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5728770</t>
+          <t>5720705</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5854493</t>
+          <t>5846032</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,51%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>103428</t>
+          <t>109793</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88599</t>
+          <t>93598</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122833</t>
+          <t>127423</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>50847</t>
+          <t>59222</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41276</t>
+          <t>48085</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61919</t>
+          <t>71410</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>154275</t>
+          <t>169015</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136360</t>
+          <t>149922</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174423</t>
+          <t>192183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>401784</t>
+          <t>440825</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>382379</t>
+          <t>423195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>416613</t>
+          <t>457020</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>396620</t>
+          <t>429189</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>385548</t>
+          <t>417001</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>406191</t>
+          <t>440326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>798404</t>
+          <t>870014</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>778256</t>
+          <t>846846</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>816319</t>
+          <t>889107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,22 +8976,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>93459</t>
+          <t>100257</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79181</t>
+          <t>84602</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110721</t>
+          <t>117785</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47499</t>
+          <t>55769</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38524</t>
+          <t>45826</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58137</t>
+          <t>67851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>140958</t>
+          <t>156026</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>123585</t>
+          <t>137004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161252</t>
+          <t>178448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -9089,27 +9089,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>357870</t>
+          <t>382033</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340608</t>
+          <t>364505</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>372148</t>
+          <t>397688</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>335081</t>
+          <t>367374</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324443</t>
+          <t>355292</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>344056</t>
+          <t>377317</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>692951</t>
+          <t>749407</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>672657</t>
+          <t>726985</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710324</t>
+          <t>768429</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451329</t>
+          <t>482290</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451329</t>
+          <t>482290</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451329</t>
+          <t>482290</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833909</t>
+          <t>905433</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833909</t>
+          <t>905433</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833909</t>
+          <t>905433</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>90055</t>
+          <t>97022</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33183</t>
+          <t>82756</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150286</t>
+          <t>114503</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38949</t>
+          <t>43449</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31598</t>
+          <t>34836</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48146</t>
+          <t>52473</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>129004</t>
+          <t>140471</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54391</t>
+          <t>123421</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>188488</t>
+          <t>160148</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>578209</t>
+          <t>374590</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517978</t>
+          <t>357109</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>635081</t>
+          <t>388856</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>127962</t>
+          <t>144048</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118765</t>
+          <t>135024</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135313</t>
+          <t>152661</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>706171</t>
+          <t>518638</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646687</t>
+          <t>498961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>780784</t>
+          <t>535688</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>81,27%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>220540</t>
+          <t>238429</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>197248</t>
+          <t>212753</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>244480</t>
+          <t>265839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>325968</t>
+          <t>133067</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>148109</t>
+          <t>117509</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>643615</t>
+          <t>149718</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>546508</t>
+          <t>371496</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>369577</t>
+          <t>340072</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1037668</t>
+          <t>402593</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>814279</t>
+          <t>893414</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>790339</t>
+          <t>866004</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>837571</t>
+          <t>919090</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>651560</t>
+          <t>727548</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>333913</t>
+          <t>710897</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>829419</t>
+          <t>743106</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1465839</t>
+          <t>1620962</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>974679</t>
+          <t>1589865</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1642770</t>
+          <t>1652386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>94128</t>
+          <t>103632</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77964</t>
+          <t>88666</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111577</t>
+          <t>121794</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>206402</t>
+          <t>221940</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155355</t>
+          <t>203048</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>240366</t>
+          <t>244104</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>300531</t>
+          <t>325572</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>243384</t>
+          <t>295535</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>331772</t>
+          <t>351104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>379921</t>
+          <t>463344</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>362472</t>
+          <t>445182</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>396085</t>
+          <t>478310</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>632594</t>
+          <t>608187</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>598630</t>
+          <t>586023</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>683641</t>
+          <t>627079</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1012514</t>
+          <t>1071531</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>981273</t>
+          <t>1045999</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1069661</t>
+          <t>1101568</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7506</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>223465</t>
+          <t>241480</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>203636</t>
+          <t>218793</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>243620</t>
+          <t>263810</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,17 +10418,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>226346</t>
+          <t>244306</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>202645</t>
+          <t>222231</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>249277</t>
+          <t>268220</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>237625</t>
+          <t>234402</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233001</t>
+          <t>229127</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239679</t>
+          <t>236288</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>536687</t>
+          <t>601513</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>516532</t>
+          <t>579183</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>556516</t>
+          <t>624200</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,17 +10531,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>774313</t>
+          <t>835915</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>751382</t>
+          <t>812001</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>798014</t>
+          <t>857990</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>604492</t>
+          <t>651959</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>463724</t>
+          <t>608416</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>668754</t>
+          <t>695865</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>893130</t>
+          <t>754928</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>714036</t>
+          <t>714121</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1409344</t>
+          <t>794898</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1497622</t>
+          <t>1406887</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1297587</t>
+          <t>1344765</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2021755</t>
+          <t>1466868</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2769688</t>
+          <t>2788607</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2705426</t>
+          <t>2744701</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2910456</t>
+          <t>2832150</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2680504</t>
+          <t>2877858</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2164290</t>
+          <t>2837888</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2859598</t>
+          <t>2918665</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5450192</t>
+          <t>5666466</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4926059</t>
+          <t>5606485</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5650227</t>
+          <t>5728588</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>80,99%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374180</t>
+          <t>3440566</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374180</t>
+          <t>3440566</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374180</t>
+          <t>3440566</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573634</t>
+          <t>3632786</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573634</t>
+          <t>3632786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573634</t>
+          <t>3632786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6947814</t>
+          <t>7073353</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6947814</t>
+          <t>7073353</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6947814</t>
+          <t>7073353</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
